--- a/medford_lineynye_datchiki_uzi.xlsx
+++ b/medford_lineynye_datchiki_uzi.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Линейные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Edan, Mindray, Siemens, Chison, SonoScape, Canon — всего 20 позиций.</t>
+          <t>Линейные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Edan, Mindray, Siemens, Chison, SonoScape, Canon.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_lineynye_datchiki_uzi.xlsx
+++ b/medford_lineynye_datchiki_uzi.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать линейные датчики УЗИ для клиники?</t>
+          <t>Для чего нужен линейный датчик УЗИ?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Количество элементов, Диапазон частот, МГц, Размер апертуры, мм, Радиус кривизны, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Линейный датчик даёт прямоугольное изображение высокого разрешения и применяется для поверхностных структур: сосудов, щитовидной железы, суставов, мягких тканей, молочных желёз, а также в педиатрии. Плоская апертура и высокая частота обеспечивают детализацию близко расположенных структур. Глубоко расположенные органы исследуют конвексными датчиками.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Как подобрать датчик к своему аппарату?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Датчик должен точно подходить к модели сканера по разъёму и программному обеспечению. Уточните марку и модель УЗИ-аппарата: датчик Mindray работает со сканером Mindray, Siemens — с Siemens. Несовместимый датчик аппарат не распознает. Совместимость проверяют до покупки, особенно для восстановленных моделей.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какой частотный диапазон выбрать?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Edan, Mindray, Siemens, Chison, SonoScape, Canon. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Частоту подбирают под задачу. Для поверхностных органов и сосудов обычно берут 5–12 МГц, для дерматологии и очень поверхностных структур — свыше 15 МГц. Высокая частота повышает разрешение, но снижает глубину проникновения. В каталоге датчики с диапазоном от 3 до 17 МГц под разные исследования.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>На что влияет число элементов?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Число элементов (в каталоге 128–256) вместе с размером апертуры определяет плотность линий сканирования и ширину поля обзора. Больше элементов — выше детализация изображения. Датчики на 256 элементов (Mindray L14-3WE, SonoScape L752) дают более плотную картинку по сравнению со 128-элементными.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Чем линейный датчик отличается от конвексного?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Линейный датчик имеет плоскую апертуру и даёт прямоугольное поле высокого разрешения для поверхностных структур на высоких частотах. Конвексный датчик с выпуклой апертурой даёт секторное поле и работает на более низких частотах для глубоко расположенных органов. Выбор зависит от исследуемой области.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,120 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Можно ли купить восстановленный датчик?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Да, в продаже есть новые и восстановленные (б/у) датчики. Восстановленные обходятся дешевле, но требуют проверки остаточного ресурса пьезоэлементов, целостности кабеля, разъёма и акустической линзы. Новые датчики поставляются с гарантией производителя. Выбор зависит от бюджета и требований к ресурсу.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>lineynye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение на датчик?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Да. Датчик УЗИ — компонент медицинского изделия, его применение в клинике в РФ требует действующего регистрационного удостоверения Росздравнадзора. Перед закупкой запросите документ на конкретную модель у поставщика и убедитесь, что он актуален.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>lineynye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Какие бренды датчиков представлены?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>В каталоге линейные датчики Edan, Mindray, Siemens, Chison, SonoScape, SIUI и Canon с числом элементов 128–256 и диапазоном частот 3–17 МГц. Датчики рассчитаны на сканеры соответствующих и совместимых платформ. Подбор ведут по модели вашего аппарата и сфере применения.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>lineynye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Линейные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Edan, Mindray, Siemens, Chison, SonoScape, Canon.</t>
+          <t>Линейные датчики УЗИ — ультразвуковые преобразователи с плоской апертурой и прямоугольным полем сканирования, применяемые для поверхностных структур: сосудов, щитовидной железы, суставов, мягких тканей и в педиатрии. В каталоге представлены датчики Edan, Mindray, Siemens, Chison, SonoScape, SIUI и Canon с количеством элементов 128–256 и диапазоном частот от 3 до 17 МГц. Высокочастотные модели (Edan L17-7Q, 7–17 МГц) дают высокое разрешение поверхностных структур. Размер апертуры варьирует от 25 до 55,5 мм. Каждый датчик рассчитан на конкретную платформу сканера.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Линейные датчики в каталоге: характеристики по моделям</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое линейные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4464,21 +4578,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Линейные датчики в каталоге: характеристики по моделям</t>
         </is>
       </c>
     </row>
@@ -4490,185 +4602,125 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Элементов</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Количество элементов</t>
+          <t>Диапазон частот, МГц</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Диапазон частот, МГц</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Размер апертуры, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Радиус кривизны, мм</t>
+          <t>Апертура, мм</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Высокочастотный линейный датчик Edan L17-7Q</t>
+          <t>Edan L17-7Q</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Edan</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>7,0-17,0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>7,0-17,0</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
+          <t>радиус 38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Линейный датчик Mindray L14-3WE</t>
+          <t>Edan L12-5Q</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>5,0-12,0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3,0-16</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>55,5</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Siemens 9L4 линейный датчик УЗИ</t>
+          <t>Mindray L14-3WE</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3,0-16</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>4-9</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>55,5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Линейный датчик Mindray L13-3N</t>
+          <t>Mindray L13-3</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3,0-14,0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>13-3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Линейный датчик Mindray L12-3E</t>
+          <t>Siemens 9L4</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>4-9</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>3,0-13,5</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4677,30 +4729,108 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Линейный датчик УЗИ Chison D7L40L</t>
+          <t>Siemens VF13-5</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Chison</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>5-13</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chison D7L40L</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>5,0-12,0</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SonoScape L752</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>4-15</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>радиус 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SIUI L10L25K</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>7-14</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Canon PLT-704AT</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>5-11</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4708,7 +4838,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4720,7 +4850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5046,12 +5176,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Уточните модель сканера</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается линейные датчики УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Линейный датчик рассчитан на конкретную платформу УЗИ-аппарата. Определите марку и модель сканера в клинике: датчик Mindray работает со сканером Mindray, Siemens — с Siemens и так далее. Совместимость по разъёму и программному обеспечению — обязательное условие, с него начинается подбор.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5091,12 +5221,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Определите область применения</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Сфера исследования задаёт частоту и геометрию датчика. Сосуды, щитовидная железа, суставы, мягкие ткани, педиатрия предъявляют разные требования. Для поверхностных органов и сосудов обычно берут диапазон 5–12 МГц, для дерматологии — свыше 15 МГц. Задача определяет выбор конкретной модели.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5136,12 +5266,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Выберите частотный диапазон</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Количество элементов, Диапазон частот, МГц, Размер апертуры, мм, Радиус кривизны, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Диапазон частот в каталоге — от 3 до 17 МГц. Высокая частота даёт лучшее разрешение поверхностных структур, но меньшую глубину проникновения. Широкополосные датчики (Siemens VF13-5, 5–13 МГц) охватывают несколько задач. Высокочастотные модели (Edan L17-7Q, 7–17 МГц) — для тонкой детализации.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5181,12 +5311,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените число элементов и апертуру</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Edan, Mindray, Siemens, Chison, SonoScape, Canon.</t>
+          <t>Число элементов в каталоге 128–256, размер апертуры 25–55,5 мм. Больше элементов и шире апертура — выше плотность линий и шире поле обзора. Компактная апертура (SIUI L10L25K, 25 мм) удобна для мелких структур и труднодоступных зон, широкая — для протяжённых областей.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5226,12 +5356,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Решите вопрос нового или б/у датчика</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Новые датчики поставляются с гарантией производителя. Восстановленные и б/у варианты требуют проверки остаточного ресурса пьезоэлементов (кристаллов) и целостности кабеля с разъёмом. При выборе б/у уточните состояние акустической линзы и историю эксплуатации.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5271,12 +5401,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте документы и совместимость финально</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Убедитесь в наличии действующего регистрационного удостоверения Росздравнадзора на датчик. Перед покупкой финально сверьте совместимость с конкретной моделью и версией ПО сканера, чтобы датчик корректно распознавался и работал во всех режимах.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5326,7 +5456,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Линейные датчики УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Edan, Mindray, Siemens, Chison, SonoScape, Canon. При выборе обращают внимание на количество элементов, диапазон частот, размер апертуры, радиус кривизны, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Линейный датчик выбирают в первую очередь по совместимости: он должен точно подходить к модели сканера по разъёму и программному обеспечению, иначе прибор его просто не увидит. Дальше смотрю на частотный диапазон под задачу — сосуды и щитовидка это одно, поверхностные структуры и дерматология другое. Число элементов и апертура определяют детализацию и ширину поля. Для восстановленных датчиков отдельно проверяю остаточный ресурс пьезоэлементов.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5610,13 +5740,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое линейные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Линейные датчики УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Edan, Mindray, Siemens, Chison, SonoScape, Canon. Подберём вариант под задачи вашего отделения.</t>
+          <t>Линейный датчик УЗИ — преобразователь с плоской апертурой, дающий прямоугольное изображение высокого разрешения для поверхностных структур: сосудов, щитовидной железы, суставов, мягких тканей, а также в педиатрии. Ключевые параметры — диапазон частот (в каталоге 3–17 МГц), число элементов (128–256) и размер апертуры (25–55,5 мм). Для поверхностных органов и сосудов обычно берут 5–12 МГц, для дерматологии — выше 15 МГц. Главное правило подбора — совместимость с моделью сканера по разъёму и ПО. В каталоге бренды Edan, Mindray, Siemens, Chison, SonoScape, SIUI, Canon.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5653,13 +5783,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое линейный датчик УЗИ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Количество элементов, Диапазон частот, МГц, Размер апертуры, мм, Радиус кривизны, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Линейный датчик — ультразвуковой преобразователь с плоской апертурой, элементы которого расположены в ряд и активируются последовательными группами. Такой принцип сканирования формирует прямоугольное изображение высокого разрешения. Датчик работает на высоких частотах и предназначен для поверхностно расположенных структур: сосудов, щитовидной железы, суставов, мягких тканей и педиатрических исследований.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5696,13 +5826,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Ключевые характеристики</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Основные параметры линейного датчика — диапазон частот (в каталоге 3–17 МГц), число элементов (128–256) и размер апертуры (25–55,5 мм). Частота определяет баланс между разрешением и глубиной проникновения, число элементов и апертура — детализацию и ширину поля обзора. Широкополосные датчики охватывают несколько задач, высокочастотные — тонкую детализацию поверхностных структур.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5739,13 +5869,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Совместимость и подбор</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Главное условие выбора — совместимость датчика с моделью сканера по разъёму и программному обеспечению; несовместимый датчик аппарат не распознает. Подбор ведут по марке и модели УЗИ-аппарата и сфере применения (сосуды, суставы, щитовидная железа). Для восстановленных датчиков дополнительно проверяют остаточный ресурс пьезоэлементов, состояние кабеля и акустической линзы.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5762,6 +5892,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Бренды в каталоге</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В каталоге представлены линейные датчики Edan, Mindray, Siemens, Chison, SonoScape, SIUI и Canon. Модели различаются числом элементов, частотным диапазоном и размером апертуры: от компактных высокочастотных (SIUI L10L25K, 7–14 МГц, апертура 25 мм) до широкоапертурных 256-элементных (Mindray L14-3WE, 3–16 МГц, апертура 55,5 мм). Датчики подбирают под конкретную платформу сканера.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>lineynye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
